--- a/docs/Mapping_casi_uso/riconoscimenti/Rico_999.xlsx
+++ b/docs/Mapping_casi_uso/riconoscimenti/Rico_999.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="700" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="707" uniqueCount="122">
   <si>
     <t>Sezione</t>
   </si>
@@ -117,6 +117,12 @@
   </si>
   <si>
     <t>descrizioneMotivoRecupero</t>
+  </si>
+  <si>
+    <t>Identificativo Atto Cartaceo</t>
+  </si>
+  <si>
+    <t>idAttoCartaceo</t>
   </si>
   <si>
     <t>Intestatario</t>
@@ -430,7 +436,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H100"/>
+  <dimension ref="A1:H101"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="19.171875" customWidth="true" bestFit="true"/>
@@ -720,62 +726,62 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="C13" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>38</v>
-      </c>
       <c r="F13" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>39</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B14" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C14" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>41</v>
-      </c>
       <c r="F14" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>42</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>43</v>
@@ -784,12 +790,12 @@
         <v>10</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>44</v>
@@ -798,7 +804,7 @@
         <v>25</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>45</v>
@@ -807,21 +813,21 @@
         <v>10</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>46</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>47</v>
@@ -830,12 +836,12 @@
         <v>10</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>48</v>
@@ -844,7 +850,7 @@
         <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>49</v>
@@ -853,12 +859,12 @@
         <v>10</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>50</v>
@@ -867,7 +873,7 @@
         <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>51</v>
@@ -876,12 +882,12 @@
         <v>10</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>52</v>
@@ -890,7 +896,7 @@
         <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>53</v>
@@ -899,21 +905,21 @@
         <v>10</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>54</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>55</v>
@@ -922,12 +928,12 @@
         <v>10</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>56</v>
@@ -936,7 +942,7 @@
         <v>25</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>57</v>
@@ -945,12 +951,12 @@
         <v>10</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>58</v>
@@ -959,7 +965,7 @@
         <v>25</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>59</v>
@@ -968,12 +974,12 @@
         <v>10</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>60</v>
@@ -982,7 +988,7 @@
         <v>25</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>61</v>
@@ -991,12 +997,12 @@
         <v>10</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>62</v>
@@ -1005,7 +1011,7 @@
         <v>25</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>63</v>
@@ -1014,21 +1020,21 @@
         <v>10</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>64</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>65</v>
@@ -1037,12 +1043,12 @@
         <v>10</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>66</v>
@@ -1051,7 +1057,7 @@
         <v>9</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>67</v>
@@ -1060,21 +1066,21 @@
         <v>10</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>69</v>
@@ -1083,12 +1089,12 @@
         <v>10</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>70</v>
@@ -1097,7 +1103,7 @@
         <v>25</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>71</v>
@@ -1106,12 +1112,12 @@
         <v>10</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>72</v>
@@ -1120,7 +1126,7 @@
         <v>25</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>73</v>
@@ -1129,12 +1135,12 @@
         <v>10</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>74</v>
@@ -1143,7 +1149,7 @@
         <v>25</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>75</v>
@@ -1152,12 +1158,12 @@
         <v>10</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>76</v>
@@ -1166,7 +1172,7 @@
         <v>25</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>77</v>
@@ -1175,12 +1181,12 @@
         <v>10</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>78</v>
@@ -1189,7 +1195,7 @@
         <v>25</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>79</v>
@@ -1198,12 +1204,12 @@
         <v>10</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>80</v>
@@ -1212,7 +1218,7 @@
         <v>25</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>81</v>
@@ -1221,12 +1227,12 @@
         <v>10</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>82</v>
@@ -1235,7 +1241,7 @@
         <v>25</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>83</v>
@@ -1244,12 +1250,12 @@
         <v>10</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>84</v>
@@ -1258,7 +1264,7 @@
         <v>25</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>85</v>
@@ -1267,12 +1273,12 @@
         <v>10</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>86</v>
@@ -1281,7 +1287,7 @@
         <v>25</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>87</v>
@@ -1290,12 +1296,12 @@
         <v>10</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>88</v>
@@ -1304,7 +1310,7 @@
         <v>25</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>89</v>
@@ -1313,12 +1319,12 @@
         <v>10</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>90</v>
@@ -1327,7 +1333,7 @@
         <v>25</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>91</v>
@@ -1336,90 +1342,90 @@
         <v>10</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B40" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="B40" s="2" t="s">
-        <v>36</v>
-      </c>
       <c r="C40" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D40" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E40" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="E40" s="2" t="s">
-        <v>38</v>
-      </c>
       <c r="F40" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B41" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="E41" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C41" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>41</v>
-      </c>
       <c r="F41" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F42" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>46</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>47</v>
@@ -1428,12 +1434,12 @@
         <v>10</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>48</v>
@@ -1442,7 +1448,7 @@
         <v>9</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>49</v>
@@ -1451,21 +1457,21 @@
         <v>10</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>94</v>
+        <v>50</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>51</v>
@@ -1474,21 +1480,21 @@
         <v>10</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>53</v>
@@ -1497,21 +1503,21 @@
         <v>10</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>55</v>
@@ -1520,21 +1526,21 @@
         <v>10</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>57</v>
@@ -1543,21 +1549,21 @@
         <v>10</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>59</v>
@@ -1566,21 +1572,21 @@
         <v>10</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>61</v>
@@ -1589,21 +1595,21 @@
         <v>10</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>62</v>
+        <v>101</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>63</v>
@@ -1612,21 +1618,21 @@
         <v>10</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>64</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>65</v>
@@ -1635,21 +1641,21 @@
         <v>10</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>100</v>
+        <v>66</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>67</v>
@@ -1658,67 +1664,67 @@
         <v>10</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>102</v>
+        <v>69</v>
       </c>
       <c r="F54" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>68</v>
+        <v>103</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>69</v>
+        <v>104</v>
       </c>
       <c r="F55" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>103</v>
+        <v>70</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>71</v>
@@ -1727,21 +1733,21 @@
         <v>10</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>73</v>
@@ -1750,21 +1756,21 @@
         <v>10</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>75</v>
@@ -1773,21 +1779,21 @@
         <v>10</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>77</v>
@@ -1796,21 +1802,21 @@
         <v>10</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>79</v>
@@ -1819,21 +1825,21 @@
         <v>10</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>81</v>
@@ -1842,21 +1848,21 @@
         <v>10</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>83</v>
@@ -1865,35 +1871,35 @@
         <v>10</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>111</v>
+        <v>85</v>
       </c>
       <c r="F63" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>112</v>
@@ -1902,7 +1908,7 @@
         <v>9</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>113</v>
@@ -1911,21 +1917,21 @@
         <v>10</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>114</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>115</v>
@@ -1934,35 +1940,35 @@
         <v>10</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>84</v>
+        <v>116</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>85</v>
+        <v>117</v>
       </c>
       <c r="F66" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>86</v>
@@ -1971,7 +1977,7 @@
         <v>25</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>87</v>
@@ -1980,12 +1986,12 @@
         <v>10</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>88</v>
@@ -1994,7 +2000,7 @@
         <v>25</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E68" s="2" t="s">
         <v>89</v>
@@ -2003,12 +2009,12 @@
         <v>10</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>90</v>
@@ -2017,7 +2023,7 @@
         <v>25</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>91</v>
@@ -2026,90 +2032,90 @@
         <v>10</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>116</v>
+        <v>94</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>36</v>
+        <v>92</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>117</v>
+        <v>95</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>38</v>
+        <v>93</v>
       </c>
       <c r="F70" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B71" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="E71" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C71" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D71" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="E71" s="2" t="s">
-        <v>41</v>
-      </c>
       <c r="F71" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F72" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>46</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>47</v>
@@ -2118,12 +2124,12 @@
         <v>10</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>48</v>
@@ -2132,7 +2138,7 @@
         <v>9</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E74" s="2" t="s">
         <v>49</v>
@@ -2141,21 +2147,21 @@
         <v>10</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>94</v>
+        <v>50</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E75" s="2" t="s">
         <v>51</v>
@@ -2164,21 +2170,21 @@
         <v>10</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E76" s="2" t="s">
         <v>53</v>
@@ -2187,21 +2193,21 @@
         <v>10</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E77" s="2" t="s">
         <v>55</v>
@@ -2210,21 +2216,21 @@
         <v>10</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E78" s="2" t="s">
         <v>57</v>
@@ -2233,21 +2239,21 @@
         <v>10</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E79" s="2" t="s">
         <v>59</v>
@@ -2256,21 +2262,21 @@
         <v>10</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E80" s="2" t="s">
         <v>61</v>
@@ -2279,21 +2285,21 @@
         <v>10</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>62</v>
+        <v>101</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E81" s="2" t="s">
         <v>63</v>
@@ -2302,21 +2308,21 @@
         <v>10</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>64</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E82" s="2" t="s">
         <v>65</v>
@@ -2325,21 +2331,21 @@
         <v>10</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>100</v>
+        <v>66</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E83" s="2" t="s">
         <v>67</v>
@@ -2348,67 +2354,67 @@
         <v>10</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>102</v>
+        <v>69</v>
       </c>
       <c r="F84" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>68</v>
+        <v>103</v>
       </c>
       <c r="C85" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>69</v>
+        <v>104</v>
       </c>
       <c r="F85" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>103</v>
+        <v>70</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E86" s="2" t="s">
         <v>71</v>
@@ -2417,21 +2423,21 @@
         <v>10</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E87" s="2" t="s">
         <v>73</v>
@@ -2440,21 +2446,21 @@
         <v>10</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C88" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E88" s="2" t="s">
         <v>75</v>
@@ -2463,21 +2469,21 @@
         <v>10</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C89" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E89" s="2" t="s">
         <v>77</v>
@@ -2486,21 +2492,21 @@
         <v>10</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C90" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E90" s="2" t="s">
         <v>79</v>
@@ -2509,21 +2515,21 @@
         <v>10</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E91" s="2" t="s">
         <v>81</v>
@@ -2532,21 +2538,21 @@
         <v>10</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E92" s="2" t="s">
         <v>83</v>
@@ -2555,35 +2561,35 @@
         <v>10</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>111</v>
+        <v>85</v>
       </c>
       <c r="F93" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B94" s="2" t="s">
         <v>112</v>
@@ -2592,7 +2598,7 @@
         <v>9</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E94" s="2" t="s">
         <v>113</v>
@@ -2601,21 +2607,21 @@
         <v>10</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B95" s="2" t="s">
         <v>114</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E95" s="2" t="s">
         <v>115</v>
@@ -2624,35 +2630,35 @@
         <v>10</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="B96" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="B96" s="2" t="s">
-        <v>84</v>
-      </c>
       <c r="C96" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D96" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="E96" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="E96" s="2" t="s">
-        <v>85</v>
-      </c>
       <c r="F96" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B97" s="2" t="s">
         <v>86</v>
@@ -2661,7 +2667,7 @@
         <v>25</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E97" s="2" t="s">
         <v>87</v>
@@ -2670,12 +2676,12 @@
         <v>10</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B98" s="2" t="s">
         <v>88</v>
@@ -2684,7 +2690,7 @@
         <v>25</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E98" s="2" t="s">
         <v>89</v>
@@ -2693,12 +2699,12 @@
         <v>10</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B99" s="2" t="s">
         <v>90</v>
@@ -2707,7 +2713,7 @@
         <v>25</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E99" s="2" t="s">
         <v>91</v>
@@ -2716,7 +2722,7 @@
         <v>10</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="100">
@@ -2724,21 +2730,44 @@
         <v>118</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>118</v>
+        <v>92</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D100" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="E100" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="F100" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G100" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D101" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E100" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="F100" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G100" s="2" t="s">
+      <c r="E101" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="F101" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G101" s="2" t="s">
         <v>16</v>
       </c>
     </row>

--- a/docs/Mapping_casi_uso/riconoscimenti/Rico_999.xlsx
+++ b/docs/Mapping_casi_uso/riconoscimenti/Rico_999.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="749" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="756" uniqueCount="128">
   <si>
     <t>Sezione</t>
   </si>
@@ -35,6 +35,18 @@
     <t>Condizioni obbligatorieta'</t>
   </si>
   <si>
+    <t>Allegati</t>
+  </si>
+  <si>
+    <t>Allegato generico</t>
+  </si>
+  <si>
+    <t>NO</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
     <t>Formula</t>
   </si>
   <si>
@@ -44,9 +56,6 @@
     <t>SI</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>Si puo' ignorare la sezione per</t>
   </si>
   <si>
@@ -87,9 +96,6 @@
   </si>
   <si>
     <t>Data decorrenza</t>
-  </si>
-  <si>
-    <t>NO</t>
   </si>
   <si>
     <t>dataDecorrenza</t>
@@ -448,7 +454,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H107"/>
+  <dimension ref="A1:H108"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="19.171875" customWidth="true" bestFit="true"/>
@@ -507,63 +513,63 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B4" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="2" t="s">
+      <c r="G4" s="1" t="s">
         <v>14</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>14</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>18</v>
@@ -572,90 +578,90 @@
         <v>10</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>19</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>26</v>
-      </c>
       <c r="F8" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>27</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>28</v>
@@ -664,21 +670,21 @@
         <v>10</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>30</v>
@@ -687,12 +693,12 @@
         <v>10</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>31</v>
@@ -701,7 +707,7 @@
         <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>32</v>
@@ -710,21 +716,21 @@
         <v>10</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>33</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>34</v>
@@ -733,21 +739,21 @@
         <v>10</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>35</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>36</v>
@@ -756,67 +762,67 @@
         <v>10</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="C14" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C14" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>40</v>
-      </c>
       <c r="F14" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>41</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B15" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C15" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>43</v>
-      </c>
       <c r="F15" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>44</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>45</v>
@@ -825,21 +831,21 @@
         <v>10</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>46</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>47</v>
@@ -848,12 +854,12 @@
         <v>10</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>48</v>
@@ -862,7 +868,7 @@
         <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>49</v>
@@ -871,21 +877,21 @@
         <v>10</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>50</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>51</v>
@@ -894,21 +900,21 @@
         <v>10</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>52</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>53</v>
@@ -917,12 +923,12 @@
         <v>10</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>54</v>
@@ -931,7 +937,7 @@
         <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>55</v>
@@ -940,21 +946,21 @@
         <v>10</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>56</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>57</v>
@@ -963,21 +969,21 @@
         <v>10</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>58</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>59</v>
@@ -986,21 +992,21 @@
         <v>10</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>60</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>61</v>
@@ -1009,21 +1015,21 @@
         <v>10</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>62</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>63</v>
@@ -1032,21 +1038,21 @@
         <v>10</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>64</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>65</v>
@@ -1055,21 +1061,21 @@
         <v>10</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>66</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>67</v>
@@ -1078,21 +1084,21 @@
         <v>10</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>69</v>
@@ -1101,12 +1107,12 @@
         <v>10</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>70</v>
@@ -1115,7 +1121,7 @@
         <v>9</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>71</v>
@@ -1124,21 +1130,21 @@
         <v>10</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>72</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>73</v>
@@ -1147,21 +1153,21 @@
         <v>10</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>74</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>75</v>
@@ -1170,21 +1176,21 @@
         <v>10</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>76</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>77</v>
@@ -1193,21 +1199,21 @@
         <v>10</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>78</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>79</v>
@@ -1216,21 +1222,21 @@
         <v>10</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>80</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>81</v>
@@ -1239,21 +1245,21 @@
         <v>10</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>82</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>83</v>
@@ -1262,21 +1268,21 @@
         <v>10</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>84</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>85</v>
@@ -1285,21 +1291,21 @@
         <v>10</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>86</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>87</v>
@@ -1308,21 +1314,21 @@
         <v>10</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>88</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>89</v>
@@ -1331,21 +1337,21 @@
         <v>10</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>90</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>91</v>
@@ -1354,21 +1360,21 @@
         <v>10</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>92</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>93</v>
@@ -1377,21 +1383,21 @@
         <v>10</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>94</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>95</v>
@@ -1400,21 +1406,21 @@
         <v>10</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>96</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>97</v>
@@ -1423,81 +1429,81 @@
         <v>10</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B43" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="B43" s="2" t="s">
-        <v>38</v>
-      </c>
       <c r="C43" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D43" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E43" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="E43" s="2" t="s">
-        <v>40</v>
-      </c>
       <c r="F43" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B44" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="E44" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C44" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>43</v>
-      </c>
       <c r="F44" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F45" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>48</v>
@@ -1506,7 +1512,7 @@
         <v>9</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>49</v>
@@ -1515,21 +1521,21 @@
         <v>10</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>50</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>51</v>
@@ -1538,21 +1544,21 @@
         <v>10</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>52</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>53</v>
@@ -1561,12 +1567,12 @@
         <v>10</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>54</v>
@@ -1575,7 +1581,7 @@
         <v>9</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>55</v>
@@ -1584,21 +1590,21 @@
         <v>10</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>100</v>
+        <v>56</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>57</v>
@@ -1607,21 +1613,21 @@
         <v>10</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>59</v>
@@ -1630,21 +1636,21 @@
         <v>10</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>61</v>
@@ -1653,21 +1659,21 @@
         <v>10</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>63</v>
@@ -1676,21 +1682,21 @@
         <v>10</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>65</v>
@@ -1699,21 +1705,21 @@
         <v>10</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>67</v>
@@ -1722,21 +1728,21 @@
         <v>10</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>68</v>
+        <v>107</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>69</v>
@@ -1745,12 +1751,12 @@
         <v>10</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>70</v>
@@ -1759,7 +1765,7 @@
         <v>9</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>71</v>
@@ -1768,21 +1774,21 @@
         <v>10</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>106</v>
+        <v>72</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>73</v>
@@ -1791,67 +1797,67 @@
         <v>10</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>108</v>
+        <v>75</v>
       </c>
       <c r="F59" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>74</v>
+        <v>109</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="F60" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>109</v>
+        <v>76</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>77</v>
@@ -1860,21 +1866,21 @@
         <v>10</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>79</v>
@@ -1883,21 +1889,21 @@
         <v>10</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>81</v>
@@ -1906,21 +1912,21 @@
         <v>10</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>83</v>
@@ -1929,21 +1935,21 @@
         <v>10</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>85</v>
@@ -1952,21 +1958,21 @@
         <v>10</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>87</v>
@@ -1975,21 +1981,21 @@
         <v>10</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>89</v>
@@ -1998,44 +2004,44 @@
         <v>10</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>117</v>
+        <v>91</v>
       </c>
       <c r="F68" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>118</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>119</v>
@@ -2044,21 +2050,21 @@
         <v>10</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>120</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>121</v>
@@ -2067,44 +2073,44 @@
         <v>10</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>90</v>
+        <v>122</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>91</v>
+        <v>123</v>
       </c>
       <c r="F71" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>92</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>93</v>
@@ -2113,21 +2119,21 @@
         <v>10</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>94</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>95</v>
@@ -2136,21 +2142,21 @@
         <v>10</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>96</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E74" s="2" t="s">
         <v>97</v>
@@ -2159,81 +2165,81 @@
         <v>10</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>122</v>
+        <v>100</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>38</v>
+        <v>98</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>123</v>
+        <v>101</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>40</v>
+        <v>99</v>
       </c>
       <c r="F75" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B76" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="E76" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C76" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D76" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="E76" s="2" t="s">
-        <v>43</v>
-      </c>
       <c r="F76" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F77" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B78" s="2" t="s">
         <v>48</v>
@@ -2242,7 +2248,7 @@
         <v>9</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E78" s="2" t="s">
         <v>49</v>
@@ -2251,21 +2257,21 @@
         <v>10</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B79" s="2" t="s">
         <v>50</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E79" s="2" t="s">
         <v>51</v>
@@ -2274,21 +2280,21 @@
         <v>10</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B80" s="2" t="s">
         <v>52</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E80" s="2" t="s">
         <v>53</v>
@@ -2297,12 +2303,12 @@
         <v>10</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>54</v>
@@ -2311,7 +2317,7 @@
         <v>9</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E81" s="2" t="s">
         <v>55</v>
@@ -2320,21 +2326,21 @@
         <v>10</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>100</v>
+        <v>56</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E82" s="2" t="s">
         <v>57</v>
@@ -2343,21 +2349,21 @@
         <v>10</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E83" s="2" t="s">
         <v>59</v>
@@ -2366,21 +2372,21 @@
         <v>10</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E84" s="2" t="s">
         <v>61</v>
@@ -2389,21 +2395,21 @@
         <v>10</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E85" s="2" t="s">
         <v>63</v>
@@ -2412,21 +2418,21 @@
         <v>10</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E86" s="2" t="s">
         <v>65</v>
@@ -2435,21 +2441,21 @@
         <v>10</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E87" s="2" t="s">
         <v>67</v>
@@ -2458,21 +2464,21 @@
         <v>10</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>68</v>
+        <v>107</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E88" s="2" t="s">
         <v>69</v>
@@ -2481,12 +2487,12 @@
         <v>10</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B89" s="2" t="s">
         <v>70</v>
@@ -2495,7 +2501,7 @@
         <v>9</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E89" s="2" t="s">
         <v>71</v>
@@ -2504,21 +2510,21 @@
         <v>10</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>106</v>
+        <v>72</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E90" s="2" t="s">
         <v>73</v>
@@ -2527,67 +2533,67 @@
         <v>10</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>108</v>
+        <v>75</v>
       </c>
       <c r="F91" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>74</v>
+        <v>109</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="F92" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>109</v>
+        <v>76</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E93" s="2" t="s">
         <v>77</v>
@@ -2596,21 +2602,21 @@
         <v>10</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E94" s="2" t="s">
         <v>79</v>
@@ -2619,21 +2625,21 @@
         <v>10</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E95" s="2" t="s">
         <v>81</v>
@@ -2642,21 +2648,21 @@
         <v>10</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E96" s="2" t="s">
         <v>83</v>
@@ -2665,21 +2671,21 @@
         <v>10</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E97" s="2" t="s">
         <v>85</v>
@@ -2688,21 +2694,21 @@
         <v>10</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E98" s="2" t="s">
         <v>87</v>
@@ -2711,21 +2717,21 @@
         <v>10</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E99" s="2" t="s">
         <v>89</v>
@@ -2734,44 +2740,44 @@
         <v>10</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C100" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>117</v>
+        <v>91</v>
       </c>
       <c r="F100" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B101" s="2" t="s">
         <v>118</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E101" s="2" t="s">
         <v>119</v>
@@ -2780,21 +2786,21 @@
         <v>10</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B102" s="2" t="s">
         <v>120</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E102" s="2" t="s">
         <v>121</v>
@@ -2803,44 +2809,44 @@
         <v>10</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B103" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="B103" s="2" t="s">
-        <v>90</v>
-      </c>
       <c r="C103" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D103" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="E103" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="E103" s="2" t="s">
-        <v>91</v>
-      </c>
       <c r="F103" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B104" s="2" t="s">
         <v>92</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E104" s="2" t="s">
         <v>93</v>
@@ -2849,21 +2855,21 @@
         <v>10</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B105" s="2" t="s">
         <v>94</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E105" s="2" t="s">
         <v>95</v>
@@ -2872,21 +2878,21 @@
         <v>10</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B106" s="2" t="s">
         <v>96</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E106" s="2" t="s">
         <v>97</v>
@@ -2895,7 +2901,7 @@
         <v>10</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="107">
@@ -2903,22 +2909,45 @@
         <v>124</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>124</v>
+        <v>98</v>
       </c>
       <c r="C107" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>14</v>
+        <v>125</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>125</v>
+        <v>99</v>
       </c>
       <c r="F107" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>16</v>
+        <v>43</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="B108" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="C108" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D108" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E108" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="F108" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G108" s="2" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
